--- a/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55558080-F68A-47BA-A584-7D3816D8021C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DF2BDEE-71F2-4E34-B2D6-58160B578B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,97 +364,97 @@
     <t>t_pos_andor</t>
   </si>
   <si>
-    <t>p_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w113757307-220_HRV</t>
+    <t>p_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Vinkovci_HRV</t>
   </si>
   <si>
     <t>OR</t>
   </si>
   <si>
-    <t>p_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>p_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>p_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>p_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>p_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>p_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>p_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>p_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>p_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>p_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>p_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>p_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>p_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>p_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>*[_]w96704507-220_HRV</t>
+    <t>p_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>p_Knin_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Knin_HRV</t>
+  </si>
+  <si>
+    <t>p_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Sisak_HRV</t>
+  </si>
+  <si>
+    <t>p_Pula_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Pula_HRV</t>
+  </si>
+  <si>
+    <t>p_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>p_Split_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Split_HRV</t>
+  </si>
+  <si>
+    <t>p_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>*[_]KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>p_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>p_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>p_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>*[_]VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>p_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>p_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>p_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Osijek_HRV</t>
+  </si>
+  <si>
+    <t>p_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>*[_]Kutina_HRV</t>
   </si>
   <si>
     <t>rez_spv_HRV_001</t>
@@ -1467,7 +1467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EECF042-41E0-434D-B6D7-EC7B63644A6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C78A754-EB1B-4CE4-A246-CC8E81627ED9}">
   <dimension ref="B9:E53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DF2BDEE-71F2-4E34-B2D6-58160B578B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABA857A8-24D0-44F2-BB11-86B77DD485F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1467,7 +1467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C78A754-EB1B-4CE4-A246-CC8E81627ED9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DD0B8B-0DDB-4E44-A6C9-5E89E9F87939}">
   <dimension ref="B9:E53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABA857A8-24D0-44F2-BB11-86B77DD485F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86F327C9-1224-4D90-BBD9-F15E6DA25BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1467,7 +1467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DD0B8B-0DDB-4E44-A6C9-5E89E9F87939}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92519533-D9C6-4050-888E-F079AFFA718C}">
   <dimension ref="B9:E53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86F327C9-1224-4D90-BBD9-F15E6DA25BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E9495C-1D56-490E-8C33-84EF0F6CC8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1467,7 +1467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92519533-D9C6-4050-888E-F079AFFA718C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D47869B2-EEE7-4624-9D8E-4D0140970A39}">
   <dimension ref="B9:E53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E9495C-1D56-490E-8C33-84EF0F6CC8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0AC630E-BAD6-4EE0-BD30-9FA66F0E5608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1467,7 +1467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D47869B2-EEE7-4624-9D8E-4D0140970A39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{546D27F7-277A-47D3-A496-4E126B42AC8E}">
   <dimension ref="B9:E53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0AC630E-BAD6-4EE0-BD30-9FA66F0E5608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F205946D-0237-4F61-8D07-91A24AFBD452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="249">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -457,6 +457,102 @@
     <t>*[_]Kutina_HRV</t>
   </si>
   <si>
+    <t>s_ogci10893_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10893_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10894_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10894_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10895_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10895_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10896_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10896_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10897_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10897_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10898_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10898_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10899_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10899_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10900_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10900_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10901_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10901_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10902_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10902_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10903_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10903_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10904_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10904_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10906_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10906_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci10907_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci10907_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci11249_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci11249_HRV</t>
+  </si>
+  <si>
+    <t>s_ogci11250_HRV</t>
+  </si>
+  <si>
+    <t>*[_]ogci11250_HRV</t>
+  </si>
+  <si>
     <t>rez_spv_HRV_001</t>
   </si>
   <si>
@@ -623,6 +719,72 @@
   </si>
   <si>
     <t>elc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>rez_wof_HRV_011</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_011</t>
   </si>
 </sst>
 </file>
@@ -1467,8 +1629,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{546D27F7-277A-47D3-A496-4E126B42AC8E}">
-  <dimension ref="B9:E53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3128B623-226D-4168-A9AC-0599ABCDF04D}">
+  <dimension ref="B9:E80"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -2089,6 +2251,384 @@
         <v>194</v>
       </c>
       <c r="E53" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>195</v>
+      </c>
+      <c r="C54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" t="s">
+        <v>196</v>
+      </c>
+      <c r="E54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>197</v>
+      </c>
+      <c r="C55" t="s">
+        <v>198</v>
+      </c>
+      <c r="D55" t="s">
+        <v>198</v>
+      </c>
+      <c r="E55" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>199</v>
+      </c>
+      <c r="C56" t="s">
+        <v>200</v>
+      </c>
+      <c r="D56" t="s">
+        <v>200</v>
+      </c>
+      <c r="E56" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" t="s">
+        <v>202</v>
+      </c>
+      <c r="D57" t="s">
+        <v>202</v>
+      </c>
+      <c r="E57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>203</v>
+      </c>
+      <c r="C58" t="s">
+        <v>204</v>
+      </c>
+      <c r="D58" t="s">
+        <v>204</v>
+      </c>
+      <c r="E58" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>205</v>
+      </c>
+      <c r="C59" t="s">
+        <v>206</v>
+      </c>
+      <c r="D59" t="s">
+        <v>206</v>
+      </c>
+      <c r="E59" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>207</v>
+      </c>
+      <c r="C60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60" t="s">
+        <v>208</v>
+      </c>
+      <c r="E60" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>209</v>
+      </c>
+      <c r="C61" t="s">
+        <v>210</v>
+      </c>
+      <c r="D61" t="s">
+        <v>210</v>
+      </c>
+      <c r="E61" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>211</v>
+      </c>
+      <c r="C62" t="s">
+        <v>212</v>
+      </c>
+      <c r="D62" t="s">
+        <v>212</v>
+      </c>
+      <c r="E62" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" t="s">
+        <v>214</v>
+      </c>
+      <c r="D63" t="s">
+        <v>214</v>
+      </c>
+      <c r="E63" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>215</v>
+      </c>
+      <c r="C64" t="s">
+        <v>216</v>
+      </c>
+      <c r="D64" t="s">
+        <v>216</v>
+      </c>
+      <c r="E64" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>217</v>
+      </c>
+      <c r="C65" t="s">
+        <v>218</v>
+      </c>
+      <c r="D65" t="s">
+        <v>218</v>
+      </c>
+      <c r="E65" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>219</v>
+      </c>
+      <c r="C66" t="s">
+        <v>220</v>
+      </c>
+      <c r="D66" t="s">
+        <v>220</v>
+      </c>
+      <c r="E66" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>221</v>
+      </c>
+      <c r="C67" t="s">
+        <v>222</v>
+      </c>
+      <c r="D67" t="s">
+        <v>222</v>
+      </c>
+      <c r="E67" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" t="s">
+        <v>224</v>
+      </c>
+      <c r="D68" t="s">
+        <v>224</v>
+      </c>
+      <c r="E68" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>225</v>
+      </c>
+      <c r="C69" t="s">
+        <v>226</v>
+      </c>
+      <c r="D69" t="s">
+        <v>226</v>
+      </c>
+      <c r="E69" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" t="s">
+        <v>228</v>
+      </c>
+      <c r="D70" t="s">
+        <v>228</v>
+      </c>
+      <c r="E70" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B71" t="s">
+        <v>229</v>
+      </c>
+      <c r="C71" t="s">
+        <v>230</v>
+      </c>
+      <c r="D71" t="s">
+        <v>230</v>
+      </c>
+      <c r="E71" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B72" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" t="s">
+        <v>232</v>
+      </c>
+      <c r="D72" t="s">
+        <v>232</v>
+      </c>
+      <c r="E72" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>233</v>
+      </c>
+      <c r="C73" t="s">
+        <v>234</v>
+      </c>
+      <c r="D73" t="s">
+        <v>234</v>
+      </c>
+      <c r="E73" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B74" t="s">
+        <v>235</v>
+      </c>
+      <c r="C74" t="s">
+        <v>236</v>
+      </c>
+      <c r="D74" t="s">
+        <v>236</v>
+      </c>
+      <c r="E74" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B75" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" t="s">
+        <v>238</v>
+      </c>
+      <c r="D75" t="s">
+        <v>238</v>
+      </c>
+      <c r="E75" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B76" t="s">
+        <v>239</v>
+      </c>
+      <c r="C76" t="s">
+        <v>240</v>
+      </c>
+      <c r="D76" t="s">
+        <v>240</v>
+      </c>
+      <c r="E76" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B77" t="s">
+        <v>241</v>
+      </c>
+      <c r="C77" t="s">
+        <v>242</v>
+      </c>
+      <c r="D77" t="s">
+        <v>242</v>
+      </c>
+      <c r="E77" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>243</v>
+      </c>
+      <c r="C78" t="s">
+        <v>244</v>
+      </c>
+      <c r="D78" t="s">
+        <v>244</v>
+      </c>
+      <c r="E78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>245</v>
+      </c>
+      <c r="C79" t="s">
+        <v>246</v>
+      </c>
+      <c r="D79" t="s">
+        <v>246</v>
+      </c>
+      <c r="E79" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" t="s">
+        <v>248</v>
+      </c>
+      <c r="D80" t="s">
+        <v>248</v>
+      </c>
+      <c r="E80" t="s">
         <v>110</v>
       </c>
     </row>

--- a/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_HRV_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F205946D-0237-4F61-8D07-91A24AFBD452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F1BD5D0-56EF-4A5E-8337-0B0B33775884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1629,7 +1629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3128B623-226D-4168-A9AC-0599ABCDF04D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C82C08D9-94CC-4A2C-BBA9-51B9C2669B8D}">
   <dimension ref="B9:E80"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
